--- a/property_management_forms/006_tenant_portal_security_survey--property_management_forms.xlsx
+++ b/property_management_forms/006_tenant_portal_security_survey--property_management_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1045,8 +1045,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="36" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="11" customWidth="1" min="2" max="2"/>
+    <col width="11" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1108,12 +1108,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>option_1</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>option1</t>
+          <t>Option 1</t>
         </is>
       </c>
     </row>
@@ -1125,12 +1125,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>option_2</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>option2</t>
+          <t>Option 2</t>
         </is>
       </c>
     </row>
@@ -1142,12 +1142,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>option_3</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>option3</t>
+          <t>Option 3</t>
         </is>
       </c>
     </row>
@@ -1159,12 +1159,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>option_4</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>option4</t>
+          <t>Option 4</t>
         </is>
       </c>
     </row>
@@ -1176,12 +1176,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>option_5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>option5</t>
+          <t>Option 5</t>
         </is>
       </c>
     </row>
@@ -1193,12 +1193,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>option_6</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>option6</t>
+          <t>Option 6</t>
         </is>
       </c>
     </row>
@@ -1244,12 +1244,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>option_7</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>option7</t>
+          <t>Option 7</t>
         </is>
       </c>
     </row>
@@ -1261,12 +1261,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>option_8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>option8</t>
+          <t>Option 8</t>
         </is>
       </c>
     </row>
@@ -1278,12 +1278,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>option_9</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>option9</t>
+          <t>Option 9</t>
         </is>
       </c>
     </row>
@@ -1295,12 +1295,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>option_10</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>option10</t>
+          <t>Option 10</t>
         </is>
       </c>
     </row>
@@ -1312,12 +1312,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>option_11</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>option11</t>
+          <t>Option 11</t>
         </is>
       </c>
     </row>
@@ -1329,12 +1329,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>option_12</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>option12</t>
+          <t>Option 12</t>
         </is>
       </c>
     </row>
@@ -1346,12 +1346,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>option_13</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>option13</t>
+          <t>Option 13</t>
         </is>
       </c>
     </row>
@@ -1363,12 +1363,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>option_14</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>option14</t>
+          <t>Option 14</t>
         </is>
       </c>
     </row>
@@ -1380,12 +1380,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>option_15</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>option15</t>
+          <t>Option 15</t>
         </is>
       </c>
     </row>
@@ -1397,12 +1397,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>option_16</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>option16</t>
+          <t>Option 16</t>
         </is>
       </c>
     </row>
@@ -1414,12 +1414,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>option_17</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>option17</t>
+          <t>Option 17</t>
         </is>
       </c>
     </row>
@@ -1431,12 +1431,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>option_18</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>option18</t>
+          <t>Option 18</t>
         </is>
       </c>
     </row>
@@ -1448,12 +1448,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>option_19</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>option19</t>
+          <t>Option 19</t>
         </is>
       </c>
     </row>
@@ -1465,12 +1465,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>option_20</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>option20</t>
+          <t>Option 20</t>
         </is>
       </c>
     </row>
@@ -1482,12 +1482,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>option_21</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>option21</t>
+          <t>Option 21</t>
         </is>
       </c>
     </row>
@@ -1499,12 +1499,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>option_22</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>option22</t>
+          <t>Option 22</t>
         </is>
       </c>
     </row>
@@ -1516,12 +1516,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>option_23</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>option23</t>
+          <t>Option 23</t>
         </is>
       </c>
     </row>
@@ -1533,12 +1533,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>option_24</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>option24</t>
+          <t>Option 24</t>
         </is>
       </c>
     </row>
